--- a/survey_templates/050_ngo_technology_capacity_survey--survey_templates.xlsx
+++ b/survey_templates/050_ngo_technology_capacity_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'some'}</t>
+          <t>some</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Some'}</t>
+          <t>Some</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'partial'}</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Partial'}</t>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'computers'}</t>
+          <t>computers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Computers'}</t>
+          <t>Computers</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'laptops'}</t>
+          <t>laptops</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Laptops'}</t>
+          <t>Laptops</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'tablets'}</t>
+          <t>tablets</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Tablets'}</t>
+          <t>Tablets</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'mobile_phones'}</t>
+          <t>mobile_phones</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Mobile Phones'}</t>
+          <t>Mobile Phones</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'fast_internet'}</t>
+          <t>fast_internet</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Fast Internet'}</t>
+          <t>Fast Internet</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium_internet'}</t>
+          <t>medium_internet</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium Internet'}</t>
+          <t>Medium Internet</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'no_internet'}</t>
+          <t>no_internet</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'No Internet'}</t>
+          <t>No Internet</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email_support'}</t>
+          <t>email_support</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Email Support'}</t>
+          <t>Email Support</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'phone_support'}</t>
+          <t>phone_support</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Phone Support'}</t>
+          <t>Phone Support</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'online_chat_support'}</t>
+          <t>online_chat_support</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Online Chat Support'}</t>
+          <t>Online Chat Support</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email_support'}</t>
+          <t>email_support</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Email Support'}</t>
+          <t>Email Support</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'phone_support'}</t>
+          <t>phone_support</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Phone Support'}</t>
+          <t>Phone Support</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'online_chat_support'}</t>
+          <t>online_chat_support</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Online Chat Support'}</t>
+          <t>Online Chat Support</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'basic_computer_training'}</t>
+          <t>basic_computer_training</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Basic Computer Training'}</t>
+          <t>Basic Computer Training</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'advanced_computer_training'}</t>
+          <t>advanced_computer_training</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Advanced Computer Training'}</t>
+          <t>Advanced Computer Training</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'firewall'}</t>
+          <t>firewall</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Firewall'}</t>
+          <t>Firewall</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'anti-virus'}</t>
+          <t>anti-virus</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Anti-virus'}</t>
+          <t>Anti-virus</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'encryption'}</t>
+          <t>encryption</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Encryption'}</t>
+          <t>Encryption</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'backup'}</t>
+          <t>backup</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Backup'}</t>
+          <t>Backup</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'local_server'}</t>
+          <t>local_server</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Local Server'}</t>
+          <t>Local Server</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'cloud_storage'}</t>
+          <t>cloud_storage</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Cloud Storage'}</t>
+          <t>Cloud Storage</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'network_admin'}</t>
+          <t>network_admin</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Network Admin'}</t>
+          <t>Network Admin</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'system_admin'}</t>
+          <t>system_admin</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'System Admin'}</t>
+          <t>System Admin</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'it_manager'}</t>
+          <t>it_manager</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'IT Manager'}</t>
+          <t>IT Manager</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'network_training'}</t>
+          <t>network_training</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Network Training'}</t>
+          <t>Network Training</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'system_training'}</t>
+          <t>system_training</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'System Training'}</t>
+          <t>System Training</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'it_training'}</t>
+          <t>it_training</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'IT Training'}</t>
+          <t>IT Training</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'expert'}</t>
+          <t>expert</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Expert'}</t>
+          <t>Expert</t>
         </is>
       </c>
     </row>
@@ -1542,12 +1542,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'software'}</t>
+          <t>software</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Software'}</t>
+          <t>Software</t>
         </is>
       </c>
     </row>
@@ -1559,12 +1559,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'hardware'}</t>
+          <t>hardware</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Hardware'}</t>
+          <t>Hardware</t>
         </is>
       </c>
     </row>
